--- a/用卷/xlsx/1958.xlsx
+++ b/用卷/xlsx/1958.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11FCE69-AB39-4400-8B1D-D8F4560B8DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C59DAF5-6A7F-47E3-9544-DFD5D8F18C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -432,7 +432,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -454,37 +454,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -537,6 +519,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -819,25 +810,25 @@
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.75" customWidth="1"/>
     <col min="4" max="4" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -849,21 +840,21 @@
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="17">
+      <c r="A4" s="11">
         <v>1958</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="30"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -872,10 +863,10 @@
       <c r="B5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="14"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -884,10 +875,10 @@
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="31"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -896,10 +887,10 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="31"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -908,20 +899,20 @@
       <c r="B8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="8"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="31"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>1958</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="31"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -930,8 +921,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="31"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
@@ -940,20 +931,20 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="9"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="31"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="10">
-        <v>1958</v>
-      </c>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="8">
+        <v>1958</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="17"/>
+      <c r="D12" s="31"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -962,10 +953,10 @@
       <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="16"/>
+      <c r="D13" s="31"/>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -974,10 +965,10 @@
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="16"/>
+      <c r="D14" s="31"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -986,10 +977,10 @@
       <c r="B15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="31"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -998,10 +989,10 @@
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="8"/>
+      <c r="D16" s="32"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
@@ -1010,36 +1001,36 @@
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="10">
-        <v>1958</v>
-      </c>
-      <c r="B18" s="10" t="s">
+      <c r="A18" s="8">
+        <v>1958</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="30"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="10">
-        <v>1958</v>
-      </c>
-      <c r="B19" s="17" t="s">
+      <c r="A19" s="8">
+        <v>1958</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="10"/>
+      <c r="D19" s="31"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
@@ -1048,10 +1039,10 @@
       <c r="B20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="8"/>
+      <c r="D20" s="31"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -1060,34 +1051,34 @@
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="31"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>1958</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="16"/>
+      <c r="D22" s="31"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>1958</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="31"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
@@ -1096,10 +1087,10 @@
       <c r="B24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="8"/>
+      <c r="D24" s="31"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
@@ -1108,10 +1099,10 @@
       <c r="B25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="12"/>
+      <c r="D25" s="31"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
@@ -1120,10 +1111,10 @@
       <c r="B26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="8"/>
+      <c r="D26" s="31"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
@@ -1132,10 +1123,10 @@
       <c r="B27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="D27" s="31"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
@@ -1144,10 +1135,10 @@
       <c r="B28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="8"/>
+      <c r="D28" s="31"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
@@ -1156,31 +1147,31 @@
       <c r="B29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="7"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="31"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
-        <v>1958</v>
-      </c>
-      <c r="B30" s="8" t="s">
+      <c r="A30" s="7">
+        <v>1958</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="32"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="6"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -1199,7 +1190,7 @@
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="5" t="s">
@@ -1211,7 +1202,7 @@
       <c r="A35" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C35" s="5" t="s">
@@ -1223,7 +1214,7 @@
       <c r="A36" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C36" s="5" t="s">
@@ -1235,7 +1226,7 @@
       <c r="A37" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C37" s="5" t="s">
@@ -1247,31 +1238,31 @@
       <c r="A38" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="18"/>
+      <c r="D38" s="12"/>
     </row>
     <row r="39" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="18"/>
+      <c r="D39" s="12"/>
     </row>
     <row r="40" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C40" s="5" t="s">
@@ -1283,7 +1274,7 @@
       <c r="A41" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C41" s="5" t="s">
@@ -1292,10 +1283,10 @@
       <c r="D41" s="6"/>
     </row>
     <row r="42" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -1303,7 +1294,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="D4:D16"/>
+    <mergeCell ref="D18:D30"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
